--- a/artfynd/A 31512-2024 artfynd.xlsx
+++ b/artfynd/A 31512-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1062,6 +1062,140 @@
       <c r="AY4" t="inlineStr">
         <is>
           <t>Norrbottens flora 2010</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122421021</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97220</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>165</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Topplåsbräken</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Botrychium lanceolatum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(S. G. Gmel.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Vägen mellan Holmträsk och Björkfors, 600 m NNV avtagsvägen mot Näverträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>878361</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7333385</v>
+      </c>
+      <c r="S5" t="n">
+        <v>100</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>BD-Kal-0192</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2004-06-21</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2004-06-21</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Vägen mellan Holmträsk och Björkfors, 600 m NNV avtagsvägen mot Näverträsk, Obskoord: 7331055/1842055/100 m (). Norrbottens flora - 2010.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>fd torpgårdsplan</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>jan Ahlm</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 31512-2024 artfynd.xlsx
+++ b/artfynd/A 31512-2024 artfynd.xlsx
@@ -1070,7 +1070,7 @@
         <v>122421021</v>
       </c>
       <c r="B5" t="n">
-        <v>97220</v>
+        <v>97232</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 31512-2024 artfynd.xlsx
+++ b/artfynd/A 31512-2024 artfynd.xlsx
@@ -1070,7 +1070,7 @@
         <v>122421021</v>
       </c>
       <c r="B5" t="n">
-        <v>97232</v>
+        <v>97237</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 31512-2024 artfynd.xlsx
+++ b/artfynd/A 31512-2024 artfynd.xlsx
@@ -1070,7 +1070,7 @@
         <v>122421021</v>
       </c>
       <c r="B5" t="n">
-        <v>97237</v>
+        <v>97246</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1084,11 +1084,6 @@
       </c>
       <c r="E5" t="n">
         <v>165</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Topplåsbräken</t>
-        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>

--- a/artfynd/A 31512-2024 artfynd.xlsx
+++ b/artfynd/A 31512-2024 artfynd.xlsx
@@ -1070,7 +1070,7 @@
         <v>122421021</v>
       </c>
       <c r="B5" t="n">
-        <v>97246</v>
+        <v>97259</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1084,6 +1084,11 @@
       </c>
       <c r="E5" t="n">
         <v>165</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Topplåsbräken</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>

--- a/artfynd/A 31512-2024 artfynd.xlsx
+++ b/artfynd/A 31512-2024 artfynd.xlsx
@@ -1070,7 +1070,7 @@
         <v>122421021</v>
       </c>
       <c r="B5" t="n">
-        <v>97259</v>
+        <v>97272</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 31512-2024 artfynd.xlsx
+++ b/artfynd/A 31512-2024 artfynd.xlsx
@@ -1070,7 +1070,7 @@
         <v>122421021</v>
       </c>
       <c r="B5" t="n">
-        <v>97272</v>
+        <v>97275</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 31512-2024 artfynd.xlsx
+++ b/artfynd/A 31512-2024 artfynd.xlsx
@@ -1070,7 +1070,7 @@
         <v>122421021</v>
       </c>
       <c r="B5" t="n">
-        <v>97275</v>
+        <v>97276</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 31512-2024 artfynd.xlsx
+++ b/artfynd/A 31512-2024 artfynd.xlsx
@@ -1070,7 +1070,7 @@
         <v>122421021</v>
       </c>
       <c r="B5" t="n">
-        <v>97276</v>
+        <v>97279</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 31512-2024 artfynd.xlsx
+++ b/artfynd/A 31512-2024 artfynd.xlsx
@@ -1070,7 +1070,7 @@
         <v>122421021</v>
       </c>
       <c r="B5" t="n">
-        <v>97279</v>
+        <v>97382</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 31512-2024 artfynd.xlsx
+++ b/artfynd/A 31512-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1062,140 +1062,6 @@
       <c r="AY4" t="inlineStr">
         <is>
           <t>Norrbottens flora 2010</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>122421021</v>
-      </c>
-      <c r="B5" t="n">
-        <v>97382</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>165</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Topplåsbräken</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Botrychium lanceolatum</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(S. G. Gmel.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Vägen mellan Holmträsk och Björkfors, 600 m NNV avtagsvägen mot Näverträsk, Nb</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>878361</v>
-      </c>
-      <c r="R5" t="n">
-        <v>7333385</v>
-      </c>
-      <c r="S5" t="n">
-        <v>100</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Kalix</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Nederkalix</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>BD-Kal-0192</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2004-06-21</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2004-06-21</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Vägen mellan Holmträsk och Björkfors, 600 m NNV avtagsvägen mot Näverträsk, Obskoord: 7331055/1842055/100 m (). Norrbottens flora - 2010.</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>fd torpgårdsplan</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Jan Yngve Andersson</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>jan Ahlm</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>
